--- a/data/trans_orig/Q5415-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5415-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2007</t>
+          <t>Población según si es capaz de salir a caminar en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19072</t>
+          <t>20899</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30789</t>
+          <t>30709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96162</t>
+          <t>95668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>109283</t>
+          <t>108589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>123533</t>
+          <t>122449</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139532</t>
+          <t>139196</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>224813</t>
+          <t>224274</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>244980</t>
+          <t>244829</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>873</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>17613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8959</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23422</t>
+          <t>23825</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37521</t>
+          <t>36868</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124594</t>
+          <t>122450</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138088</t>
+          <t>138115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149528</t>
+          <t>149733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167287</t>
+          <t>167983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>279823</t>
+          <t>280546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>301738</t>
+          <t>303033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21468</t>
+          <t>20734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92385</t>
+          <t>92159</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101635</t>
+          <t>101762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111402</t>
+          <t>111675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126833</t>
+          <t>126468</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208217</t>
+          <t>206913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225826</t>
+          <t>225287</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15113</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18602</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30655</t>
+          <t>30882</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36096</t>
+          <t>34789</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>124720</t>
+          <t>124839</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133946</t>
+          <t>133999</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>168663</t>
+          <t>168583</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>188798</t>
+          <t>188884</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>296836</t>
+          <t>297523</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>321099</t>
+          <t>320618</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>21828</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42942</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27734</t>
+          <t>27633</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53037</t>
+          <t>52381</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20906</t>
+          <t>21587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41512</t>
+          <t>41519</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40189</t>
+          <t>41741</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69914</t>
+          <t>69606</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>67918</t>
+          <t>67379</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>104490</t>
+          <t>102809</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>452714</t>
+          <t>452426</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>474734</t>
+          <t>474765</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>573141</t>
+          <t>573959</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>609438</t>
+          <t>608800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1035031</t>
+          <t>1036994</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1077761</t>
+          <t>1078503</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2012</t>
+          <t>Población según si es capaz de salir a caminar en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>20985</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>9429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>24845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23701</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32146</t>
+          <t>30439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>124410</t>
+          <t>124201</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>135510</t>
+          <t>135601</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>127648</t>
+          <t>128211</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>147381</t>
+          <t>147495</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257206</t>
+          <t>257289</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>281059</t>
+          <t>281124</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>14995</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34026</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20943</t>
+          <t>20791</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42729</t>
+          <t>41720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>23840</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33325</t>
+          <t>34430</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>25232</t>
+          <t>25997</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>49414</t>
+          <t>50383</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123499</t>
+          <t>123366</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142361</t>
+          <t>141850</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>132060</t>
+          <t>131679</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156087</t>
+          <t>156212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>262058</t>
+          <t>263592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292889</t>
+          <t>293402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28503</t>
+          <t>28068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16756</t>
+          <t>16560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40401</t>
+          <t>38689</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23415</t>
+          <t>24041</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12615</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28338</t>
+          <t>29119</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81441</t>
+          <t>82334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98062</t>
+          <t>98202</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95883</t>
+          <t>96259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116738</t>
+          <t>117078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184390</t>
+          <t>185049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>211809</t>
+          <t>211029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,27%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24760</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31485</t>
+          <t>30362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22301</t>
+          <t>22116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11374</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>28749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23084</t>
+          <t>23089</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47122</t>
+          <t>45508</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132699</t>
+          <t>133778</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150297</t>
+          <t>150556</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>196079</t>
+          <t>196072</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>219096</t>
+          <t>218042</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>335577</t>
+          <t>336491</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>363346</t>
+          <t>364150</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35592</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54309</t>
+          <t>54820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89035</t>
+          <t>86674</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76081</t>
+          <t>73900</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>113511</t>
+          <t>114411</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>48498</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57764</t>
+          <t>58899</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>90451</t>
+          <t>93624</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>91036</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>131499</t>
+          <t>131923</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>483320</t>
+          <t>483955</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>514973</t>
+          <t>514056</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>576082</t>
+          <t>577264</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>621151</t>
+          <t>620995</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1074094</t>
+          <t>1070977</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1125241</t>
+          <t>1125797</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,43%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2016</t>
+          <t>Población según si es capaz de salir a caminar en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>11650</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14897</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>22107</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>13295</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31853</t>
+          <t>31422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>18896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38741</t>
+          <t>39303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117771</t>
+          <t>116467</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130016</t>
+          <t>129607</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133751</t>
+          <t>133596</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>154263</t>
+          <t>155048</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257250</t>
+          <t>256490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>281890</t>
+          <t>280924</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>19121</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18147</t>
+          <t>17275</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>19054</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41911</t>
+          <t>40557</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26471</t>
+          <t>27767</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52102</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142470</t>
+          <t>142316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156436</t>
+          <t>156360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>170243</t>
+          <t>171992</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195906</t>
+          <t>195777</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320696</t>
+          <t>319419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>348771</t>
+          <t>348654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25946</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>12032</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30798</t>
+          <t>31669</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27202</t>
+          <t>26668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13248</t>
+          <t>13823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32027</t>
+          <t>33295</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99763</t>
+          <t>99247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>110621</t>
+          <t>111075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96874</t>
+          <t>95143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118891</t>
+          <t>118227</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>200374</t>
+          <t>200809</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>226356</t>
+          <t>226372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11045</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21983</t>
+          <t>20866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>27062</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13801</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34410</t>
+          <t>34511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43263</t>
+          <t>42940</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>154872</t>
+          <t>153939</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>167662</t>
+          <t>167972</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>195581</t>
+          <t>194986</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>220722</t>
+          <t>220577</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>355328</t>
+          <t>356918</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>384987</t>
+          <t>384473</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27763</t>
+          <t>28584</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27509</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56057</t>
+          <t>57206</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44815</t>
+          <t>44881</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75923</t>
+          <t>77370</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19642</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40089</t>
+          <t>39270</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70333</t>
+          <t>71610</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108314</t>
+          <t>108757</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96106</t>
+          <t>97923</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>139683</t>
+          <t>140756</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>531103</t>
+          <t>531396</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>555099</t>
+          <t>555910</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>624085</t>
+          <t>624004</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>670383</t>
+          <t>670012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1164826</t>
+          <t>1164210</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1217009</t>
+          <t>1216266</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2023</t>
+          <t>Población según si es capaz de salir a caminar en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10091</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26327</t>
+          <t>27107</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20358</t>
+          <t>20352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33681</t>
+          <t>33969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>9174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20082</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21981</t>
+          <t>21323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33898</t>
+          <t>33686</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33260</t>
+          <t>33543</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50326</t>
+          <t>50384</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121333</t>
+          <t>121129</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134559</t>
+          <t>134376</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>123645</t>
+          <t>123078</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>138875</t>
+          <t>139085</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>249313</t>
+          <t>249240</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>269053</t>
+          <t>269159</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,25%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23088</t>
+          <t>24357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17594</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31245</t>
+          <t>29355</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>18491</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>25791</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40314</t>
+          <t>41771</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35584</t>
+          <t>35758</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55297</t>
+          <t>54771</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>136304</t>
+          <t>135268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148477</t>
+          <t>147816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159388</t>
+          <t>159842</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176657</t>
+          <t>177033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>300103</t>
+          <t>299510</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>321082</t>
+          <t>321017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,83%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>874</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36547</t>
+          <t>37417</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33603</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14435</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46164</t>
+          <t>47571</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48697</t>
+          <t>49687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117576</t>
+          <t>117459</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129448</t>
+          <t>130056</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>279938</t>
+          <t>277668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>352548</t>
+          <t>351728</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>417261</t>
+          <t>416551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>484661</t>
+          <t>482465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22946</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16579</t>
+          <t>16482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30476</t>
+          <t>30060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30251</t>
+          <t>30308</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47392</t>
+          <t>46266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39855</t>
+          <t>40623</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59470</t>
+          <t>60918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>180995</t>
+          <t>182044</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193408</t>
+          <t>193483</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>209263</t>
+          <t>210407</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>229027</t>
+          <t>230507</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>395996</t>
+          <t>394985</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>419474</t>
+          <t>418581</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15089</t>
+          <t>14018</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28645</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36935</t>
+          <t>38425</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91213</t>
+          <t>91914</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60481</t>
+          <t>61282</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109030</t>
+          <t>109599</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>35187</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57670</t>
+          <t>56521</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61377</t>
+          <t>64041</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>151635</t>
+          <t>150500</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>105578</t>
+          <t>106753</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>192158</t>
+          <t>190979</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>570957</t>
+          <t>570107</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>595510</t>
+          <t>595297</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>794833</t>
+          <t>793464</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>934241</t>
+          <t>928126</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1387129</t>
+          <t>1387219</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1515594</t>
+          <t>1516315</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5415-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5415-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>12680</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>19859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30709</t>
+          <t>30734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95668</t>
+          <t>96947</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>108589</t>
+          <t>108563</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>122449</t>
+          <t>122709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139196</t>
+          <t>139406</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>224274</t>
+          <t>223212</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>244829</t>
+          <t>244770</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16032</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17613</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>18366</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8959</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23825</t>
+          <t>25744</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36868</t>
+          <t>37456</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122450</t>
+          <t>124317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138115</t>
+          <t>138227</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149733</t>
+          <t>147323</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167983</t>
+          <t>167567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280546</t>
+          <t>280236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>303033</t>
+          <t>302634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16750</t>
+          <t>16773</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17774</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20734</t>
+          <t>21401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92159</t>
+          <t>91974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101762</t>
+          <t>101665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111675</t>
+          <t>111486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126468</t>
+          <t>126401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>206913</t>
+          <t>208517</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225287</t>
+          <t>225655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>815</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6704</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>16083</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>19766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13320</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30882</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34789</t>
+          <t>36191</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>124839</t>
+          <t>125153</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133999</t>
+          <t>133961</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>168583</t>
+          <t>169001</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>188884</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>297523</t>
+          <t>297915</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>320618</t>
+          <t>320126</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>13499</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21828</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43824</t>
+          <t>43463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>27584</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>52381</t>
+          <t>52078</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21587</t>
+          <t>22376</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41519</t>
+          <t>42056</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>41741</t>
+          <t>41935</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69606</t>
+          <t>71939</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>67379</t>
+          <t>67625</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102809</t>
+          <t>102420</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>452426</t>
+          <t>451397</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>474765</t>
+          <t>473541</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>573959</t>
+          <t>571277</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>608800</t>
+          <t>606747</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1036994</t>
+          <t>1033966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1078503</t>
+          <t>1076477</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20985</t>
+          <t>21428</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9429</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>25047</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24469</t>
+          <t>24128</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30439</t>
+          <t>31097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>124201</t>
+          <t>123355</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>135601</t>
+          <t>135567</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>128211</t>
+          <t>127957</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>147495</t>
+          <t>148179</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257289</t>
+          <t>257986</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>281124</t>
+          <t>280867</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14357</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33621</t>
+          <t>32891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20791</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41720</t>
+          <t>43385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>22764</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34430</t>
+          <t>33166</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>25997</t>
+          <t>25570</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50383</t>
+          <t>49313</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123366</t>
+          <t>123926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141850</t>
+          <t>141830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131679</t>
+          <t>132131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156212</t>
+          <t>155926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263592</t>
+          <t>263102</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293402</t>
+          <t>293091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>17810</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28068</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>17510</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38689</t>
+          <t>38436</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>9801</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24041</t>
+          <t>23547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29119</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82334</t>
+          <t>81760</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98202</t>
+          <t>98160</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96259</t>
+          <t>96618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>117078</t>
+          <t>117450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>185049</t>
+          <t>187485</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>211029</t>
+          <t>211299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>10829</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>24699</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30362</t>
+          <t>31023</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22116</t>
+          <t>22617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>12044</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28749</t>
+          <t>29219</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23089</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45508</t>
+          <t>45094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>133778</t>
+          <t>133116</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150556</t>
+          <t>150183</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>196072</t>
+          <t>196740</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>218042</t>
+          <t>217848</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>336491</t>
+          <t>336208</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>364150</t>
+          <t>364315</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54820</t>
+          <t>54005</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86674</t>
+          <t>87406</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73900</t>
+          <t>75643</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114411</t>
+          <t>113347</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24470</t>
+          <t>24491</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48498</t>
+          <t>49110</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58899</t>
+          <t>56640</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93624</t>
+          <t>90763</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>91036</t>
+          <t>88762</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>131923</t>
+          <t>128922</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>483955</t>
+          <t>483579</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>514056</t>
+          <t>514774</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>577264</t>
+          <t>578757</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>620995</t>
+          <t>619559</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1070977</t>
+          <t>1076362</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1125797</t>
+          <t>1128499</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11650</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22107</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31422</t>
+          <t>31743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39303</t>
+          <t>38804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116467</t>
+          <t>117550</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129607</t>
+          <t>130427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133596</t>
+          <t>134121</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155048</t>
+          <t>154007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256490</t>
+          <t>256513</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>280924</t>
+          <t>280738</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>13444</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19121</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17275</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19054</t>
+          <t>18714</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40557</t>
+          <t>40054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27767</t>
+          <t>27547</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>54493</t>
+          <t>53594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142316</t>
+          <t>142530</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156360</t>
+          <t>156385</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>171992</t>
+          <t>173032</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195777</t>
+          <t>195545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>319419</t>
+          <t>320898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>348654</t>
+          <t>348495</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>27552</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12766</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31669</t>
+          <t>32114</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26668</t>
+          <t>26810</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13823</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33295</t>
+          <t>33604</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99247</t>
+          <t>99819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111075</t>
+          <t>111109</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95143</t>
+          <t>96824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118227</t>
+          <t>117631</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>200809</t>
+          <t>200053</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>226372</t>
+          <t>226279</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,83%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>21811</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27062</t>
+          <t>27892</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>14532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34511</t>
+          <t>34834</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19998</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42940</t>
+          <t>43262</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>153939</t>
+          <t>153936</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>167972</t>
+          <t>167717</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>194986</t>
+          <t>195672</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>220577</t>
+          <t>221183</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>356918</t>
+          <t>356493</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>384473</t>
+          <t>384644</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12050</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>29377</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57206</t>
+          <t>58165</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>45126</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77370</t>
+          <t>77009</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39270</t>
+          <t>39016</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71610</t>
+          <t>69706</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108757</t>
+          <t>107686</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>97923</t>
+          <t>97042</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140756</t>
+          <t>138322</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>531396</t>
+          <t>531107</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>555910</t>
+          <t>555383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>624004</t>
+          <t>626192</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>670012</t>
+          <t>670607</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1164210</t>
+          <t>1166110</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1216266</t>
+          <t>1216752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -8264,22 +8264,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20741</t>
+          <t>22155</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15799</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27107</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>26151</t>
+          <t>28042</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>21354</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33969</t>
+          <t>35642</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27308</t>
+          <t>29154</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>22838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33686</t>
+          <t>36196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>41329</t>
+          <t>43766</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33543</t>
+          <t>35777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50384</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>128653</t>
+          <t>142815</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121129</t>
+          <t>135434</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134376</t>
+          <t>149140</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>131113</t>
+          <t>139720</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>123078</t>
+          <t>131388</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139085</t>
+          <t>147585</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>259766</t>
+          <t>282535</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>249240</t>
+          <t>272015</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>269159</t>
+          <t>292739</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,61%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>19391</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>13662</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24357</t>
+          <t>25996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>23079</t>
+          <t>25431</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>18803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29355</t>
+          <t>33827</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>19156</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32595</t>
+          <t>36432</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>29086</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41771</t>
+          <t>45503</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>48954</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35758</t>
+          <t>39459</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>54771</t>
+          <t>59502</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>142592</t>
+          <t>159642</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135268</t>
+          <t>151891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147816</t>
+          <t>165348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>168307</t>
+          <t>185751</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159842</t>
+          <t>175042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177033</t>
+          <t>194432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>310900</t>
+          <t>345393</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>299510</t>
+          <t>333165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>321017</t>
+          <t>356778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,99%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218312</t>
+          <t>241574</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218312</t>
+          <t>241574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218312</t>
+          <t>241574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378427</t>
+          <t>419778</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378427</t>
+          <t>419778</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378427</t>
+          <t>419778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>15592</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37417</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>17898</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>12890</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34411</t>
+          <t>28695</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14008</t>
+          <t>15965</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18249</t>
+          <t>20428</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47571</t>
+          <t>27878</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>26589</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49687</t>
+          <t>39228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>124821</t>
+          <t>146292</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117459</t>
+          <t>138483</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130056</t>
+          <t>151744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>327334</t>
+          <t>138293</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>277668</t>
+          <t>129407</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>351728</t>
+          <t>146036</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>452156</t>
+          <t>284585</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>416551</t>
+          <t>273750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>482465</t>
+          <t>294676</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>359691</t>
+          <t>174313</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>359691</t>
+          <t>174313</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>359691</t>
+          <t>174313</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>496643</t>
+          <t>334098</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>496643</t>
+          <t>334098</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>496643</t>
+          <t>334098</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16820</t>
+          <t>18755</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11408</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22770</t>
+          <t>25149</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16482</t>
+          <t>18490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30060</t>
+          <t>34863</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>17542</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38616</t>
+          <t>42734</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30308</t>
+          <t>34303</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46266</t>
+          <t>52802</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>49671</t>
+          <t>54143</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40623</t>
+          <t>44371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60918</t>
+          <t>64705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>188024</t>
+          <t>197286</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182044</t>
+          <t>190227</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193483</t>
+          <t>202744</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>220187</t>
+          <t>233877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>210407</t>
+          <t>222228</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>230507</t>
+          <t>243970</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>408212</t>
+          <t>431162</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>394985</t>
+          <t>418068</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>418581</t>
+          <t>443101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>20819</t>
+          <t>22452</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14018</t>
+          <t>15903</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>32943</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>69079</t>
+          <t>75893</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38425</t>
+          <t>63673</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91914</t>
+          <t>89519</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>89898</t>
+          <t>98345</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>61282</t>
+          <t>84740</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109599</t>
+          <t>113478</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45269</t>
+          <t>47905</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35187</t>
+          <t>37214</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56521</t>
+          <t>59240</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>116768</t>
+          <t>128747</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64041</t>
+          <t>113801</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>150500</t>
+          <t>146819</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>162037</t>
+          <t>176652</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>106753</t>
+          <t>160166</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>190979</t>
+          <t>197085</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>584090</t>
+          <t>646034</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>570107</t>
+          <t>631946</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>595297</t>
+          <t>658736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>846944</t>
+          <t>697642</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>793464</t>
+          <t>677392</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>928126</t>
+          <t>716271</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1431034</t>
+          <t>1343676</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1387219</t>
+          <t>1320771</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1516315</t>
+          <t>1363311</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1032791</t>
+          <t>902282</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1032791</t>
+          <t>902282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1032791</t>
+          <t>902282</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1682969</t>
+          <t>1618673</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1682969</t>
+          <t>1618673</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1682969</t>
+          <t>1618673</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
